--- a/137532_Cuenca_San_Juan/_raw_reportes_xlsx/IDConfig_2356_completo.xlsx
+++ b/137532_Cuenca_San_Juan/_raw_reportes_xlsx/IDConfig_2356_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R528949db324d4bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R22411d6367c3464a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Ica / Prov: Chincha / Dist.: Alto Laran</x:t>
+          <x:t>Dpto: Ica / Prov: Chincha / Dist.: Alto Larán</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -250,6 +250,81 @@
         <x:is>
           <x:t>VALOR (m³/s)</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9130</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9950</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/137532_Cuenca_San_Juan/_raw_reportes_xlsx/IDConfig_2356_completo.xlsx
+++ b/137532_Cuenca_San_Juan/_raw_reportes_xlsx/IDConfig_2356_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R22411d6367c3464a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5560fc59bf044039"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,486 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0490</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3890</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1330</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3570</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2940</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
